--- a/Item/ItemBulkImportTemplate.xlsx
+++ b/Item/ItemBulkImportTemplate.xlsx
@@ -627,22 +627,22 @@
   </sheetData>
   <autoFilter ref="A1:M1"/>
   <dataValidations count="6">
-    <dataValidation sqref="F2:F501" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed value" error="Pick one of: Default, Product, Raw Material, Packaging Material, Work in Progress, Semi-Finished Goods, Auxiliary Material" type="list">
+    <dataValidation sqref="F2:F1001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed value" error="Pick one of: Default, Product, Raw Material, Packaging Material, Work in Progress, Semi-Finished Goods, Auxiliary Material" type="list">
       <formula1>"Default,Product,Raw Material,Packaging Material,Work in Progress,Semi-Finished Goods,Auxiliary Material"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G501" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed value" error="Pick one of: Goods, Services" type="list">
+    <dataValidation sqref="G2:G1001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed value" error="Pick one of: Goods, Services" type="list">
       <formula1>"Goods,Services"</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H501" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed value" error="Pick one of: Yes, No" type="list">
+    <dataValidation sqref="H2:H1001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed value" error="Pick one of: Yes, No" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="I2:I501" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed value" error="Pick one of: Yes, No" type="list">
+    <dataValidation sqref="I2:I1001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed value" error="Pick one of: Yes, No" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="L2:L501" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed value" error="Pick one of: Yes, No" type="list">
+    <dataValidation sqref="L2:L1001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed value" error="Pick one of: Yes, No" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M501" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed value" error="Pick one of: According To System Settings, Manual Input" type="list">
+    <dataValidation sqref="M2:M1001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed value" error="Pick one of: According To System Settings, Manual Input" type="list">
       <formula1>"According To System Settings,Manual Input"</formula1>
     </dataValidation>
   </dataValidations>
